--- a/cad/rig_v2/Partlist_v2.xlsx
+++ b/cad/rig_v2/Partlist_v2.xlsx
@@ -1,19 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tallA\Repos\VolumanXR\hardware-capture\cad\rig_v2\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86E5511-8C2D-4988-B07A-BCE014C50EE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="-28920" yWindow="-10785" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Stückliste" sheetId="1" r:id="rId2"/>
+    <sheet name="Stückliste" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="125725" fullCalcOnLoad="true"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="80" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="93">
   <si>
     <t>Objekt</t>
   </si>
@@ -42,6 +49,54 @@
     <t>REV.</t>
   </si>
   <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
@@ -75,6 +130,57 @@
     <t>11</t>
   </si>
   <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>14AWG-RED.Draht7</t>
+  </si>
+  <si>
+    <t>14AWG-RED.Draht16</t>
+  </si>
+  <si>
+    <t>14AWG-RED.Draht9</t>
+  </si>
+  <si>
+    <t>14AWG-RED.Draht13</t>
+  </si>
+  <si>
+    <t>14AWG-RED.Draht5</t>
+  </si>
+  <si>
+    <t>14AWG-RED.Draht1</t>
+  </si>
+  <si>
+    <t>14AWG-RED.Draht3</t>
+  </si>
+  <si>
+    <t>14AWG-RED.Draht11</t>
+  </si>
+  <si>
+    <t>14AWG-RED.Draht8</t>
+  </si>
+  <si>
+    <t>14AWG-RED.Draht15</t>
+  </si>
+  <si>
+    <t>14AWG-RED.Draht10</t>
+  </si>
+  <si>
+    <t>14AWG-RED.Draht14</t>
+  </si>
+  <si>
+    <t>14AWG-RED.Draht6</t>
+  </si>
+  <si>
+    <t>14AWG-RED.Draht2</t>
+  </si>
+  <si>
+    <t>14AWG-RED.Draht4</t>
+  </si>
+  <si>
+    <t>14AWG-RED.Draht12</t>
+  </si>
+  <si>
     <t>Profil_5_40x40_2500</t>
   </si>
   <si>
@@ -108,7 +214,13 @@
     <t>Zentrierplattensatz_5</t>
   </si>
   <si>
-    <t>(NichtAnzeigbar)</t>
+    <t>DIN 9021 - 5,3</t>
+  </si>
+  <si>
+    <t>(NULL)</t>
+  </si>
+  <si>
+    <t>*Verschieden*</t>
   </si>
   <si>
     <t>Normal</t>
@@ -117,9 +229,60 @@
     <t>Gekauft</t>
   </si>
   <si>
+    <t>1577,992 mm</t>
+  </si>
+  <si>
+    <t>1549,536 mm</t>
+  </si>
+  <si>
+    <t>1497,747 mm</t>
+  </si>
+  <si>
+    <t>1492,999 mm</t>
+  </si>
+  <si>
+    <t>1475,572 mm</t>
+  </si>
+  <si>
+    <t>1474,589 mm</t>
+  </si>
+  <si>
+    <t>1410,227 mm</t>
+  </si>
+  <si>
+    <t>1390,726 mm</t>
+  </si>
+  <si>
+    <t>893,520 mm</t>
+  </si>
+  <si>
+    <t>854,765 mm</t>
+  </si>
+  <si>
+    <t>805,482 mm</t>
+  </si>
+  <si>
+    <t>782,957 mm</t>
+  </si>
+  <si>
+    <t>780,312 mm</t>
+  </si>
+  <si>
+    <t>761,843 mm</t>
+  </si>
+  <si>
+    <t>709,954 mm</t>
+  </si>
+  <si>
+    <t>660,243 mm</t>
+  </si>
+  <si>
     <t>Jede</t>
   </si>
   <si>
+    <t>14AWG-RED</t>
+  </si>
+  <si>
     <t>STEP AP214</t>
   </si>
   <si>
@@ -130,6 +293,9 @@
   </si>
   <si>
     <t>Innensechskant-Rundkopfschraube - Produktklasse A</t>
+  </si>
+  <si>
+    <t>Unterlegscheibe</t>
   </si>
   <si>
     <t xml:space="preserve"> NONE</t>
@@ -138,8 +304,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -166,11 +332,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -178,41 +344,54 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1724025</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>1724025</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="true"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
@@ -234,24 +413,30 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1724025</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>1724025</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2"/>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="true"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
@@ -273,24 +458,30 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1724025</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>1724025</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3"/>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="true"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
@@ -312,24 +503,30 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1724025</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>1724025</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4"/>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="true"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId4"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
@@ -351,24 +548,30 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1724025</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>1724025</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5"/>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="true"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
@@ -390,24 +593,30 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1724025</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>1724025</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6"/>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="true"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
@@ -429,24 +638,30 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1724025</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>1724025</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 7"/>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="true"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId7"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
@@ -468,24 +683,30 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1724025</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>1724025</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8"/>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="true"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId8"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
@@ -507,24 +728,30 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1724025</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>1724025</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 9"/>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="true"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId9"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
@@ -546,24 +773,30 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1724025</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>1724025</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 10"/>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="true"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId10"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
@@ -585,24 +818,30 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1724025</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>1724025</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Picture 11"/>
+        <xdr:cNvPr id="12" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="true"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId11"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
@@ -623,15 +862,332 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I128"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.35546875" customWidth="true"/>
+    <col min="2" max="2" width="30.85546875" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -660,242 +1216,641 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="68.25" customHeight="true" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="F2" s="1">
         <v>4</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" ht="68.25" customHeight="true" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>21</v>
+        <v>38</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="F3" s="1">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" ht="68.25" customHeight="true" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>39</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="F4" s="1">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" ht="68.25" customHeight="true" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>23</v>
+        <v>40</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="F5" s="1">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" ht="68.25" customHeight="true" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>24</v>
+        <v>41</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="F6" s="1">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" ht="68.25" customHeight="true" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>42</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="F7" s="1">
-        <v>384</v>
+        <v>4</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" ht="68.25" customHeight="true" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>43</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="F8" s="1">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" ht="68.25" customHeight="true" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>44</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="F9" s="1">
-        <v>384</v>
+        <v>4</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" ht="68.25" customHeight="true" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>28</v>
+        <v>45</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="F10" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" ht="68.25" customHeight="true" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>46</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>34</v>
+        <v>78</v>
       </c>
       <c r="F11" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" ht="68.25" customHeight="true" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F12" s="1">
+        <v>4</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F13" s="1">
+        <v>4</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" s="1">
+        <v>4</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F15" s="1">
+        <v>4</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F16" s="1">
+        <v>4</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F17" s="1">
+        <v>4</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F18" s="1">
+        <v>4</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F19" s="1">
+        <v>29</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F20" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F21" s="1">
+        <v>22</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F22" s="1">
+        <v>32</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="B23" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F23" s="1">
+        <v>448</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F24" s="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="B25" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F25" s="1">
+        <v>448</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F26" s="1">
+        <v>2</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F12" s="1">
+      <c r="B27" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F28" s="1">
         <v>2</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
+      <c r="H28" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F29" s="1">
+        <v>64</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="122" ht="68.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="68.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="68.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="68.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="68.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="68.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="68.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/cad/rig_v2/Partlist_v2.xlsx
+++ b/cad/rig_v2/Partlist_v2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tallA\Repos\VolumanXR\hardware-capture\cad\rig_v2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aldi\Repos\VolumanXR\hardware-capture\cad\rig_v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86E5511-8C2D-4988-B07A-BCE014C50EE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB62D37-85DB-4F05-B37F-755D6063AD0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-10785" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stückliste" sheetId="1" r:id="rId1"/>
@@ -1180,14 +1180,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I128"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="30.85546875" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" customWidth="1"/>
-    <col min="5" max="5" width="16.5703125" customWidth="1"/>
+    <col min="2" max="2" width="30.88671875" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="5" max="5" width="16.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1216,7 +1216,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -1285,7 +1285,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -1308,7 +1308,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -1331,7 +1331,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -1354,7 +1354,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
@@ -1423,7 +1423,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
@@ -1492,7 +1492,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>21</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>22</v>
       </c>
@@ -1538,7 +1538,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>24</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
@@ -1600,6 +1600,9 @@
       <c r="F18" s="1">
         <v>4</v>
       </c>
+      <c r="G18">
+        <v>4</v>
+      </c>
       <c r="H18" s="1" t="s">
         <v>87</v>
       </c>
@@ -1607,7 +1610,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>26</v>
       </c>
@@ -1623,6 +1626,9 @@
       <c r="F19" s="1">
         <v>29</v>
       </c>
+      <c r="G19">
+        <v>29</v>
+      </c>
       <c r="H19" s="1" t="s">
         <v>87</v>
       </c>
@@ -1630,7 +1636,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
@@ -1647,7 +1653,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>28</v>
       </c>
@@ -1663,6 +1669,9 @@
       <c r="F21" s="1">
         <v>22</v>
       </c>
+      <c r="G21">
+        <v>22</v>
+      </c>
       <c r="H21" s="1" t="s">
         <v>87</v>
       </c>
@@ -1670,7 +1679,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>29</v>
       </c>
@@ -1693,7 +1702,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>30</v>
       </c>
@@ -1719,7 +1728,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>31</v>
       </c>
@@ -1736,7 +1745,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>32</v>
       </c>
@@ -1756,7 +1765,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>33</v>
       </c>
@@ -1772,6 +1781,9 @@
       <c r="F26" s="1">
         <v>2</v>
       </c>
+      <c r="G26">
+        <v>2</v>
+      </c>
       <c r="H26" s="1" t="s">
         <v>87</v>
       </c>
@@ -1779,7 +1791,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>34</v>
       </c>
@@ -1795,6 +1807,9 @@
       <c r="F27" s="1">
         <v>1</v>
       </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
       <c r="H27" s="1" t="s">
         <v>87</v>
       </c>
@@ -1802,7 +1817,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>35</v>
       </c>
@@ -1822,7 +1837,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>36</v>
       </c>
@@ -1842,13 +1857,13 @@
         <v>91</v>
       </c>
     </row>
-    <row r="122" ht="68.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="68.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="68.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="68.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="68.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="68.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="68.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="68.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="123" ht="68.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="124" ht="68.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="125" ht="68.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="126" ht="68.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="127" ht="68.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="128" ht="68.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
